--- a/cfg/excel/SceneCfg.xlsx
+++ b/cfg/excel/SceneCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29670" windowHeight="17640"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,9 +17,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -57,6 +57,18 @@
     <t>movePos</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>battleType</t>
+  </si>
+  <si>
+    <t>rewards</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -72,6 +84,12 @@
     <t>(list#sep=|),vector3</t>
   </si>
   <si>
+    <t>BattleType</t>
+  </si>
+  <si>
+    <t>(list#sep=,),ItemData</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -87,37 +105,268 @@
     <t>移动位置</t>
   </si>
   <si>
+    <t>场景名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>战斗类型</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
     <t>Battle1</t>
   </si>
   <si>
-    <t>5.4,-17.6,327.5|6.9,-17.6,0|6.9,-15.5,0_12,15.7,90.5|13.6,15.7,0|13.5,17.9,0</t>
-  </si>
-  <si>
-    <t>6.1,2.5,0|-5.8,3.6,0|10.1,8,0</t>
+    <t>3.4,-15.4,0|5.4,-14.5,23.3|3.3,-14.7,298.1_11.4,13.7,220.5|12.4,12.5,101.8|13.9,14.6,182.4_-11.5,14.8,187.9|-12.3,13.1,196.4|-9.9,13.4,122.6_-14.6,0.4,270|-12.8,1,235.9|-13.5,-0.6,315.2_15.5,6.9,145.8|15.2,4.6,63.1|16.5,5.3,90_14.5,-11.1,90|13,-12.6,0|14.4,-13.3,0_-10.4,-12.9,0|-9.4,-13.3,0|-9.6,-13.9,0_1.2,13.5,180|2.7,12.3,180|1.4,11.4,180</t>
+  </si>
+  <si>
+    <t>4.3,-9.8,0|3.2,-1.1,0|-0.5,-6.4,0|1,-8.4,0|4.7,-7.2,0|-6.1,-3.4,0|-9.5,-4.5,0|-10.7,0.3,0|-9,-2.1,0|-11.2,3.7,0|-11.4,-2.2,0|-13.8,-3.1,0|-15.1,3.5,0|-6,-11.9,0|-3.6,-14.5,0|-4.6,-9.1,0|-12.8,-9,0|-7.9,-7.2,0|-4,-7.7,0|3.1,-11.3,0|0.3,-10,0|1.6,-2.8,0|7.5,-4.7,0|8.8,-7.9,0|10.7,-14.2,0|8.6,-11.3,0|12.3,-9.4,0|16.6,-8.5,0|13,-7.7,0|15.5,-5.2,0|13.1,-3.1,0|12.4,2.8,0|15.3,12.8,0|10.7,7.7,0|12.4,16.2,0|15.5,10.9,0|12.4,10.8,0|15.4,2.3,0|12.8,5.2,0|12.9,-1,0|5.1,15.5,0|4.3,10.7,0|6.2,8.8,0|2.7,14.4,0|-2.3,9.5,0|-4.6,12,0|-11.6,8,0|-7.9,11.4,0|-14.6,12.1,0|-11.9,11.8,0|-7.4,14.2,0|-7.8,-9.9,0|-9.8,-10.4,0|-2.4,-11.2,0|-12.5,-14.4,0|-4.7,2.6,0|-3.1,4.8,0|-4.9,6,0|6.6,1.3,0|4.1,2,0|-2.7,-1.8,0|0,-4.6,0|8.7,-0.3,0|-0.2,4.5,0|5.2,3.7,0|5.2,5.1,0|8.3,4.4,0|8.2,6,0|2.6,7.4,0|-0.6,6.7,0|-4.7,8.9,0|-8.2,5.6,0</t>
+  </si>
+  <si>
+    <t>-7.7,4.4,0|-4.7,6.4,0|-4.8,3.1,0|-3.1,4.4,0|-0.7,6.4,0|-0.6,4,0|3.9,7.5,0|3.3,1.8,0|3.1,-0.5,0|5.2,4.3,0|6.7,1.6,0|7.2,6.1,0|8.2,3.9,0|8.7,-0.7,0|-0.6,-4,0|-3.3,-1.4,0|0.5,-7.8,0|7.2,-7.5,0|-3.9,-6.9,0|10.5,-5.8,0|-4.7,15.1,0|2.9,-12.3,0|5.5,-11.3,0|-1.3,-12.1,0|-5.8,-12.4,0|-3.8,-14.2,0|-12.9,-11.3,0|-9.4,-7.4,0|-3.3,-9.1,0|8.5,-11.6,0|13.7,-9.3,0|12.9,-14.2,0|15.1,-4.6,0|12.4,-5.3,0|13.9,-0.9,0|12.8,3.6,0|15.2,1.4,0|13.5,9,0|13.4,11.2,0|4.1,9.4,0|5.3,13.4,0|2.8,14.9,0|7.4,14.7,0|-1.6,12.3,0|-9.7,8.7,0|-12.8,9.4,0|-8,10.8,0|-7.5,13.7,0|-14.7,11.4,0|-11.5,2.8,0|-8.9,-2.8,0|-15,-2.6,0|-12.9,-4.4,0|-13.7,3.8,0</t>
+  </si>
+  <si>
+    <t>1号大坝</t>
+  </si>
+  <si>
+    <t>PVP</t>
+  </si>
+  <si>
+    <t>1_11,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>2号大坝</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3号大坝</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4号大坝</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>5号大坝</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>6号大坝</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>7号大坝</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>8号大坝</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>9号大坝</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10号大坝</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>11号大坝</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Battle2</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Battle3</t>
-  </si>
-  <si>
-    <t>3.4,-15.4,0|5.4,-14.5,23.3|3.3,-14.7,298.1_11.4,13.7,220.5|12.4,12.5,101.8|13.9,14.6,182.4_-11.5,14.8,187.9|-12.3,13.1,196.4|-9.9,13.4,122.6_-14.6,0.4,270|-12.8,1,235.9|-13.5,-0.6,315.2_15.5,6.9,145.8|15.2,4.6,63.1|16.5,5.3,90_14.5,-11.1,90|13,-12.6,0|14.4,-13.3,0_-10.4,-12.9,0|-9.4,-13.3,0|-9.6,-13.9,0_1.2,13.5,180|2.7,12.3,180|1.4,11.4,180</t>
-  </si>
-  <si>
-    <t>4.3,-9.8,0|3.2,-1.1,0|-0.5,-6.4,0|1,-8.4,0|4.7,-7.2,0|-6.1,-3.4,0|-9.5,-4.5,0|-10.7,0.3,0|-9,-2.1,0|-11.2,3.7,0|-11.4,-2.2,0|-13.8,-3.1,0|-15.1,3.5,0|-6,-11.9,0|-3.6,-14.5,0|-4.6,-9.1,0|-12.8,-9,0|-7.9,-7.2,0|-4,-7.7,0|3.1,-11.3,0|0.3,-10,0|1.6,-2.8,0|7.5,-4.7,0|8.8,-7.9,0|10.7,-14.2,0|8.6,-11.3,0|12.3,-9.4,0|16.6,-8.5,0|13,-7.7,0|15.5,-5.2,0|13.1,-3.1,0|12.4,2.8,0|15.3,12.8,0|10.7,7.7,0|12.4,16.2,0|15.5,10.9,0|12.4,10.8,0|15.4,2.3,0|12.8,5.2,0|12.9,-1,0|5.1,15.5,0|4.3,10.7,0|6.2,8.8,0|2.7,14.4,0|-2.3,9.5,0|-4.6,12,0|-11.6,8,0|-7.9,11.4,0|-14.6,12.1,0|-11.9,11.8,0|-7.4,14.2,0|-7.8,-9.9,0|-9.8,-10.4,0|-2.4,-11.2,0|-12.5,-14.4,0|-4.7,2.6,0|-3.1,4.8,0|-4.9,6,0|6.6,1.3,0|4.1,2,0|-2.7,-1.8,0|0,-4.6,0|8.7,-0.3,0|-0.2,4.5,0|5.2,3.7,0|5.2,5.1,0|8.3,4.4,0|8.2,6,0|2.6,7.4,0|-0.6,6.7,0|-4.7,8.9,0|-8.2,5.6,0</t>
-  </si>
-  <si>
-    <t>-7.7,4.4,0|-4.7,6.4,0|-4.8,3.1,0|-3.1,4.4,0|-0.7,6.4,0|-0.6,4,0|3.9,7.5,0|3.3,1.8,0|3.1,-0.5,0|5.2,4.3,0|6.7,1.6,0|7.2,6.1,0|8.2,3.9,0|8.7,-0.7,0|-0.6,-4,0|-3.3,-1.4,0|0.5,-7.8,0|7.2,-7.5,0|-3.9,-6.9,0|10.5,-5.8,0|-4.7,15.1,0|2.9,-12.3,0|5.5,-11.3,0|-1.3,-12.1,0|-5.8,-12.4,0|-3.8,-14.2,0|-12.9,-11.3,0|-9.4,-7.4,0|-3.3,-9.1,0|8.5,-11.6,0|13.7,-9.3,0|12.9,-14.2,0|15.1,-4.6,0|12.4,-5.3,0|13.9,-0.9,0|12.8,3.6,0|15.2,1.4,0|13.5,9,0|13.4,11.2,0|4.1,9.4,0|5.3,13.4,0|2.8,14.9,0|7.4,14.7,0|-1.6,12.3,0|-9.7,8.7,0|-12.8,9.4,0|-8,10.8,0|-7.5,13.7,0|-14.7,11.4,0|-11.5,2.8,0|-8.9,-2.8,0|-15,-2.6,0|-12.9,-4.4,0|-13.7,3.8,0</t>
+    <t>PVE</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>12号大坝</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>13号大坝</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>14号大坝</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>15号大坝</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>16号大坝</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>17号大坝</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>18号大坝</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>19号大坝</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20号大坝</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>21号大坝</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>22号大坝</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>23号大坝</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>24号大坝</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>25号大坝</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>26号大坝</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>27号大坝</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>28号大坝</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>29号大坝</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>30号大坝</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>31号大坝</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>32号大坝</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>33号大坝</t>
   </si>
 </sst>
 </file>
@@ -125,16 +374,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -142,23 +392,27 @@
       <sz val="14"/>
       <color theme="0"/>
       <name val="黑体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -166,12 +420,14 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -179,6 +435,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -186,6 +443,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -193,6 +451,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -200,6 +459,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -207,12 +467,14 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,6 +482,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -227,6 +490,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,12 +498,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -247,30 +513,35 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -606,19 +877,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -751,171 +1022,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="2" applyBorder="1" xfId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" xfId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" xfId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" xfId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="28">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="29">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="30">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="31">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="32">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="33">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="34">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="35">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="36">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="37">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="38">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="39">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="40">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="41">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="42">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="43">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="44">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="45">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="46">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="1" xfId="47">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="1" xfId="48">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1228,127 +1349,1234 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="2" width="10.5" customWidth="1" style="52"/>
-    <col min="3" max="3" width="18.25" customWidth="1" style="52"/>
-    <col min="4" max="4" width="44.625" customWidth="1" style="52"/>
-    <col min="5" max="5" width="57.375" customWidth="1" style="52"/>
-    <col min="6" max="6" width="46.25" customWidth="1" style="52"/>
-    <col min="7" max="7" width="10.5" customWidth="1" style="52"/>
-    <col min="8" max="8" width="11.75" customWidth="1" style="52"/>
-    <col min="9" max="9" width="11.625" customWidth="1" style="52"/>
-    <col min="10" max="16384" width="9" customWidth="1" style="52"/>
+    <col min="1" max="2" width="10.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="44.625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="57.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="46.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="15.75" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="33.875" style="3" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="50" customFormat="1">
-      <c r="A1" s="50" t="s">
+    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" s="51" customFormat="1">
-      <c r="A2" s="51" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="51" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="51" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="52" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="52" t="s">
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="52" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="53" t="s">
+      <c r="E3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="52" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="53" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="52" t="s">
+      <c r="I3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="52" t="s">
+      <c r="J3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="52" t="s">
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="F7" s="54"/>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1360,6 +2588,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1371,6 +2600,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cfg/excel/SceneCfg.xlsx
+++ b/cfg/excel/SceneCfg.xlsx
@@ -17,9 +17,9 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t>##var</t>
   </si>
@@ -51,7 +51,7 @@
     <t>teamPos</t>
   </si>
   <si>
-    <t>itemPos</t>
+    <t>collectionPos</t>
   </si>
   <si>
     <t>movePos</t>
@@ -81,6 +81,9 @@
     <t>(list#sep=_),TeamPos</t>
   </si>
   <si>
+    <t>(list#sep=|),CollectionPos</t>
+  </si>
+  <si>
     <t>(list#sep=|),vector3</t>
   </si>
   <si>
@@ -123,25 +126,31 @@
     <t>Battle1</t>
   </si>
   <si>
+    <t>15.3,14.5,200.7|15.9,13.6,144.9|15.8,14.1,232_-11.5,14.8,187.9|-12,14,196.4|-10.6,14,122.6_14.5,-14,112.9|13,-14.6,326.6|13.9,-14.6,16.3_-13.2,-14,310.4|-13.5,-14.5,322.6|-12.2,-14,23.9</t>
+  </si>
+  <si>
+    <t>0.6,2,0_1001,1004,1005,1006</t>
+  </si>
+  <si>
+    <t>-7.7,4.4,0|-4.7,6.4,0|-4.8,3.1,0|-3.1,4.4,0|-0.7,6.4,0|0,4.6,0|3.9,7.5,0|3.3,1.8,0|3.1,-0.5,0|5.2,4.3,0|6.7,1.6,0|7.2,6.1,0|8.2,3.9,0|8.7,-0.7,0|-0.6,-4,0|-3.3,-1.4,0|0.5,-7.8,0|7.2,-7.5,0|-3.9,-6.9,0|10.5,-5.8,0|-4.7,15.1,0|2.9,-12.3,0|5.5,-11.3,0|-1.3,-12.1,0|-5.8,-12.4,0|-3.8,-14.2,0|-12.9,-11.3,0|-9.4,-7.4,0|-3.3,-9.1,0|8.5,-11.6,0|13.7,-9.3,0|12.9,-14.2,0|15.1,-4.6,0|12.4,-5.3,0|13.9,-0.9,0|12.8,3.6,0|15.2,1.4,0|13.5,9,0|13.4,11.2,0|4.1,9.4,0|5.3,13.4,0|2.8,14.9,0|7.4,14.7,0|-1.6,12.3,0|-9.7,8.7,0|-12.8,9.4,0|-8,10.8,0|-7.5,13.7,0|-14.7,11.4,0|-11.5,2.8,0|-8.9,-2.8,0|-15,-2.6,0|-12.9,-4.4,0|-13.7,3.8,0</t>
+  </si>
+  <si>
+    <t>1号大坝</t>
+  </si>
+  <si>
+    <t>PVP</t>
+  </si>
+  <si>
+    <t>1_11,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>3.4,-15.4,0|5.4,-14.5,23.3|3.3,-14.7,298.1_11.4,13.7,220.5|12.4,12.5,101.8|13.9,14.6,182.4_-11.5,14.8,187.9|-12.3,13.1,196.4|-9.9,13.4,122.6_-14.6,0.4,270|-12.8,1,235.9|-13.5,-0.6,315.2_15.5,6.9,145.8|15.2,4.6,63.1|16.5,5.3,90_14.5,-11.1,90|13,-12.6,0|14.4,-13.3,0_-10.4,-12.9,0|-9.4,-13.3,0|-9.6,-13.9,0_1.2,13.5,180|2.7,12.3,180|1.4,11.4,180</t>
   </si>
   <si>
-    <t>4.3,-9.8,0|3.2,-1.1,0|-0.5,-6.4,0|1,-8.4,0|4.7,-7.2,0|-6.1,-3.4,0|-9.5,-4.5,0|-10.7,0.3,0|-9,-2.1,0|-11.2,3.7,0|-11.4,-2.2,0|-13.8,-3.1,0|-15.1,3.5,0|-6,-11.9,0|-3.6,-14.5,0|-4.6,-9.1,0|-12.8,-9,0|-7.9,-7.2,0|-4,-7.7,0|3.1,-11.3,0|0.3,-10,0|1.6,-2.8,0|7.5,-4.7,0|8.8,-7.9,0|10.7,-14.2,0|8.6,-11.3,0|12.3,-9.4,0|16.6,-8.5,0|13,-7.7,0|15.5,-5.2,0|13.1,-3.1,0|12.4,2.8,0|15.3,12.8,0|10.7,7.7,0|12.4,16.2,0|15.5,10.9,0|12.4,10.8,0|15.4,2.3,0|12.8,5.2,0|12.9,-1,0|5.1,15.5,0|4.3,10.7,0|6.2,8.8,0|2.7,14.4,0|-2.3,9.5,0|-4.6,12,0|-11.6,8,0|-7.9,11.4,0|-14.6,12.1,0|-11.9,11.8,0|-7.4,14.2,0|-7.8,-9.9,0|-9.8,-10.4,0|-2.4,-11.2,0|-12.5,-14.4,0|-4.7,2.6,0|-3.1,4.8,0|-4.9,6,0|6.6,1.3,0|4.1,2,0|-2.7,-1.8,0|0,-4.6,0|8.7,-0.3,0|-0.2,4.5,0|5.2,3.7,0|5.2,5.1,0|8.3,4.4,0|8.2,6,0|2.6,7.4,0|-0.6,6.7,0|-4.7,8.9,0|-8.2,5.6,0</t>
-  </si>
-  <si>
     <t>-7.7,4.4,0|-4.7,6.4,0|-4.8,3.1,0|-3.1,4.4,0|-0.7,6.4,0|-0.6,4,0|3.9,7.5,0|3.3,1.8,0|3.1,-0.5,0|5.2,4.3,0|6.7,1.6,0|7.2,6.1,0|8.2,3.9,0|8.7,-0.7,0|-0.6,-4,0|-3.3,-1.4,0|0.5,-7.8,0|7.2,-7.5,0|-3.9,-6.9,0|10.5,-5.8,0|-4.7,15.1,0|2.9,-12.3,0|5.5,-11.3,0|-1.3,-12.1,0|-5.8,-12.4,0|-3.8,-14.2,0|-12.9,-11.3,0|-9.4,-7.4,0|-3.3,-9.1,0|8.5,-11.6,0|13.7,-9.3,0|12.9,-14.2,0|15.1,-4.6,0|12.4,-5.3,0|13.9,-0.9,0|12.8,3.6,0|15.2,1.4,0|13.5,9,0|13.4,11.2,0|4.1,9.4,0|5.3,13.4,0|2.8,14.9,0|7.4,14.7,0|-1.6,12.3,0|-9.7,8.7,0|-12.8,9.4,0|-8,10.8,0|-7.5,13.7,0|-14.7,11.4,0|-11.5,2.8,0|-8.9,-2.8,0|-15,-2.6,0|-12.9,-4.4,0|-13.7,3.8,0</t>
-  </si>
-  <si>
-    <t>1号大坝</t>
-  </si>
-  <si>
-    <t>PVP</t>
-  </si>
-  <si>
-    <t>1_11,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100,2_100</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>2号大坝</t>
@@ -384,7 +393,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -392,27 +400,23 @@
       <sz val="14"/>
       <color theme="0"/>
       <name val="黑体"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="黑体"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -420,14 +424,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -435,7 +437,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -443,7 +444,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -451,7 +451,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -459,7 +458,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,14 +465,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -482,7 +478,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -490,7 +485,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -498,14 +492,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -513,35 +505,30 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1022,20 +1009,167 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="54">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="4" applyFill="1" borderId="2" applyBorder="1" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="5" applyBorder="1" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" applyFill="1" borderId="9" applyBorder="1" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="20" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="1" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="21" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="1" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1352,1230 +1486,1146 @@
   <dimension ref="A1:J46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="2" width="10.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="18.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="44.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="46.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.75" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.5" style="3" customWidth="1"/>
-    <col min="10" max="10" width="33.875" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="2" width="10.5" customWidth="1" style="52"/>
+    <col min="3" max="3" width="18.25" customWidth="1" style="52"/>
+    <col min="4" max="4" width="44.625" customWidth="1" style="52"/>
+    <col min="5" max="5" width="57.375" customWidth="1" style="52"/>
+    <col min="6" max="6" width="46.25" customWidth="1" style="52"/>
+    <col min="7" max="7" width="15.75" customWidth="1" style="52"/>
+    <col min="8" max="8" width="11.75" customWidth="1" style="52"/>
+    <col min="9" max="9" width="22.5" customWidth="1" style="52"/>
+    <col min="10" max="10" width="33.875" customWidth="1" style="52"/>
+    <col min="11" max="16384" width="9" customWidth="1" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22" customHeight="1" s="50" customFormat="1">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:10">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="51" customFormat="1">
+      <c r="A2" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="51" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="J2" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="I3" s="52" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="B4" s="4" t="s">
+      <c r="J3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="4">
+      <c r="B4" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="G4" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="I4" s="52" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="J4" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="D5" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="52" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="J5" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="D6" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="52" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
+      <c r="J6" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="4" t="s">
+      <c r="I15" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="4" t="s">
+      <c r="I16" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="s">
+      <c r="I17" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="4" t="s">
+      <c r="I18" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="4" t="s">
+      <c r="I19" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="4" t="s">
+      <c r="I20" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="4" t="s">
+      <c r="I21" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="53" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="4" t="s">
+      <c r="I22" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="I23" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="I24" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="4" t="s">
+      <c r="C25" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="I25" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" s="4" t="s">
+      <c r="C26" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="I26" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="4" t="s">
+      <c r="C27" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="I27" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J27" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="4" t="s">
+      <c r="C28" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="I28" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31" s="4" t="s">
+      <c r="C29" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="I29" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="4" t="s">
+      <c r="C30" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="I30" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J30" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33" s="4" t="s">
+      <c r="C31" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="I31" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J31" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" s="4" t="s">
+      <c r="C32" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="I32" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J32" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" s="4" t="s">
+      <c r="C33" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="52" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="I33" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J33" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" s="4" t="s">
+      <c r="C34" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="52" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="I34" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J34" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37" s="4" t="s">
+      <c r="C35" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="I35" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J35" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38" s="4" t="s">
+      <c r="C36" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G36" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="I36" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39" s="4" t="s">
+      <c r="C37" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G37" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G39" s="3" t="s">
+      <c r="I37" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J37" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
-      <c r="B40" s="4" t="s">
+      <c r="C38" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G38" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="3" t="s">
+      <c r="I38" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J38" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="B41" s="4" t="s">
+      <c r="C39" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G39" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="I39" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J39" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="4" t="s">
+      <c r="C40" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="I40" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" s="4" t="s">
+      <c r="C41" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E41" s="52"/>
+      <c r="F41" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" s="3" t="s">
+      <c r="I41" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J41" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" s="4" t="s">
+      <c r="C42" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D42" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G42" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="I42" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J42" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="4" t="s">
+      <c r="C43" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G43" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="I43" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="4" t="s">
+      <c r="C44" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G46" s="3" t="s">
+      <c r="I44" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J44" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>33</v>
+      <c r="C45" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G45" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="I45" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J45" s="52" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="53" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I46" s="52" t="s">
+        <v>59</v>
+      </c>
+      <c r="J46" s="52" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2588,7 +2638,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2600,7 +2649,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
